--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -520,10 +520,10 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -602,35 +602,55 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>use_rf_pulse</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rf_pulse_power</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rf_pulse_freq</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rf_pulse_duty</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>gun1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gun2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>G1 Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>G2 Target</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>use_heater</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>heater_temp</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>heater_ramp</t>
         </is>
@@ -657,13 +677,13 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="5" t="n"/>
-      <c r="U2" s="5" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
+      <c r="W2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+      <c r="Y2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -718,35 +738,35 @@
       <c r="N3" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="n">
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="U3" s="5" t="n">
+      <c r="Y3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -801,35 +821,35 @@
         </is>
       </c>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="n">
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="U4" s="5" t="n">
+      <c r="Y4" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -884,33 +904,130 @@
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>SiO2_RFpulse_300C</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="n">
+        <v>30</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -923,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -1099,341 +1216,418 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
+          <t xml:space="preserve">   use_rf_pulse       RF Pulse(CESAR) 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
+          <t xml:space="preserve">   rf_pulse_power     RF Pulse 파워 [W]. use_rf_pulse=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      상한은 config_user.json 의 RFPULSE_MAX_POWER (현재 600W) 입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>■ 히터 컬럼 3개</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   rf_pulse_freq      펄스 주파수 [kHz]</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
+          <t xml:space="preserve">   rf_pulse_duty      펄스 듀티 [%]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
+          <t xml:space="preserve">   ★ use_rf_power 와 use_rf_pulse 는 동시에 켤 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
+          <t xml:space="preserve">     RF power 는 PLC DAC, RF Pulse 는 CESAR 로 서로 다른 장비이고,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+          <t xml:space="preserve">     화면의 for.P / ref.P 칸을 함께 쓰기 때문입니다. 둘 다 T 면 오류로 거부합니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 PLC 램프는 1카운트/초 = 6°C/min 단위라 6의 배수로 반올림됩니다 (10 → 12).</t>
+          <t xml:space="preserve">   ★ rf_pulse_freq / rf_pulse_duty 를 비우면 장비에 현재 설정된 값을 그대로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ★ 히터 레시피(히터 전용 파일)에 있는 '느린 램프(6 미만)' 는 공정 레시피에는 없습니다.</t>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     이때도 공정 로그와 ChK_log.csv 에는 장비에서 되읽은 실제 값이 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 이 4개 컬럼이 아예 없는 옛 레시피는 자동으로 펄스 미사용이 됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>■ 히터를 쓰면 공정이 이 순서로 진행됩니다</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
+          <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
-        </is>
-      </c>
+      <c r="A39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>■ 히터 컬럼 3개</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
+          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
+          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
+          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
+          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
+          <t xml:space="preserve">                 PLC 램프는 1카운트/초 = 6°C/min 단위라 6의 배수로 반올림됩니다 (10 → 12).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 히터 레시피(히터 전용 파일)에 있는 '느린 램프(6 미만)' 는 공정 레시피에는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
-        </is>
-      </c>
+      <c r="A47" s="7" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>■ 히터를 쓰면 공정이 이 순서로 진행됩니다</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
+          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
+          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
+          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n"/>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
+          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n"/>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>■ 도달 대기 타임아웃</t>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
+          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
+          <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n"/>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
+          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
+          <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
-        </is>
-      </c>
+      <c r="A63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
+          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+          <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
-        </is>
-      </c>
+      <c r="A66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>■ 도달 대기 타임아웃</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
+          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
-        </is>
-      </c>
+      <c r="A70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n"/>
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>■ 저장할 때</t>
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
+          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>■ 저장할 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · 레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행은 넣지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="7" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>작성 2026-09-04 · 관련 설정: config_user.json 의 HEATER_* 항목</t>
         </is>

--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1029,6 +1029,95 @@
         <v>12</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SiO2_RF+Pulse</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X7" s="5" t="n"/>
+      <c r="Y7" s="5" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1040,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -1251,7 +1340,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ use_rf_power 와 use_rf_pulse 는 동시에 켤 수 없습니다.</t>
+          <t xml:space="preserve">   ★ use_rf_power / use_rf_pulse / use_dc_power 는 서로 독립이며 동시에 켤 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1354,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     화면의 for.P / ref.P 칸을 함께 쓰기 때문입니다. 둘 다 T 면 오류로 거부합니다.</t>
+          <t xml:space="preserve">     화면 칸도 ChK_log.csv 컬럼도 각자 따로 갖습니다.</t>
         </is>
       </c>
     </row>
@@ -1293,191 +1382,195 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
+          <t xml:space="preserve">   ★ ChK_log.csv 에는 RF Pulse 전용 4컬럼이 따로 남습니다:</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
+          <t xml:space="preserve">     "RF Pulse: For.P" / "RF Pulse: Ref. P" (계측 평균), "RF Pulse: Freq[kHz]" / "RF Pulse: Duty[%]" (설정값)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n"/>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     기존 "RF: For.P" / "RF: Ref. P" 는 계속 RF power(PLC DAC) 전용입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>■ 히터 컬럼 3개</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
+          <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
-        </is>
-      </c>
+      <c r="A42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>■ 히터 컬럼 3개</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">                 PLC 램프는 1카운트/초 = 6°C/min 단위라 6의 배수로 반올림됩니다 (10 → 12).</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ 히터 레시피(히터 전용 파일)에 있는 '느린 램프(6 미만)' 는 공정 레시피에는 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="7" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>■ 히터를 쓰면 공정이 이 순서로 진행됩니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
+          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
+          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
+          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
+          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
+          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
+          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
+          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
+          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
+          <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n"/>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
+          <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
         </is>
       </c>
     </row>
@@ -1485,149 +1578,166 @@
       <c r="A66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>■ 도달 대기 타임아웃</t>
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>■ 도달 대기 타임아웃</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
+          <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
-        </is>
-      </c>
+      <c r="A73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
+          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="7" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>■ 저장할 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · 레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행은 넣지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="7" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>작성 2026-09-04 · 관련 설정: config_user.json 의 HEATER_* 항목</t>
         </is>

--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0E+00"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
@@ -136,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,6 +161,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -524,23 +529,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="7"/>
-    <col width="9" customWidth="1" min="8" max="9"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="7"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="21"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="18"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="21"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1">
@@ -556,115 +573,120 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>base_pressure</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>working_pressure</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>process_time</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>shutter_delay</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ar</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ar_flow</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>O2_flow</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>use_dc_power</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dc_power</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>use_dc_delay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>use_rf_power</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rf_power</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>use_rf_pulse</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_power</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_freq</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_duty</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gun1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>gun2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>G1 Target</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>G2 Target</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>use_heater</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>heater_temp</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>heater_ramp</t>
         </is>
@@ -679,79 +701,82 @@
           <t>SiO2_RF_300C</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="12" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="X2" s="5" t="n">
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="Y2" s="5" t="n">
+      <c r="Z2" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -764,75 +789,78 @@
           <t>Au_no_heat</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="12" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N3" s="3" t="n"/>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="n"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X3" s="5" t="n"/>
       <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -843,91 +871,94 @@
           <t>SiO2_RFpulse_300C</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="12" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>200</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>50</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="X4" s="5" t="n">
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="Y4" s="5" t="n">
+      <c r="Z4" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -940,85 +971,88 @@
           <t>SiO2_RF+Pulse</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="12" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>100</v>
       </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>SiO2</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="W5" s="5" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="X5" s="5" t="n"/>
       <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1031,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A92"/>
+  <dimension ref="A1:A93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="108" customWidth="1" min="1" max="1"/>
@@ -1123,523 +1157,530 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   working_pressure   작업 압력 [mTorr]. 필수, 0 보다 커야 합니다.</t>
+          <t xml:space="preserve">   base_pressure      베이스 압력 [Torr]. 가스를 넣기 전 이온 게이지로 이 값 이하가 될 때까지 기다립니다. 비우거나 열이 없으면 1E-5, 0 이면 대기 생략, 1E-9 ~ 1E-3 (1e-5 / 1.0E-05 / 숫자 모두 가능).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   process_time       증착 시간 [분].</t>
+          <t xml:space="preserve">   working_pressure   작업 압력 [mTorr]. 필수, 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   process_time       증착 시간 [분].</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   shutter_delay      셔터 대기 시간 [분]. 비우면 0.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ process_time 과 shutter_delay 중 하나는 반드시 0 보다 커야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Ar / O2            가스 사용 여부. 둘 중 하나 이상 T 여야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ar_flow / O2_flow  유량 [sccm]. 해당 가스가 T 면 0 보다 커야 합니다.</t>
+          <t xml:space="preserve">   Ar / O2            가스 사용 여부. 둘 중 하나 이상 T 여야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_dc_power       DC 파워 사용 여부</t>
+          <t xml:space="preserve">   Ar_flow / O2_flow  유량 [sccm]. 해당 가스가 T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   dc_power           DC 파워 [W]. use_dc_power=T 면 0 보다 커야 합니다.</t>
+          <t xml:space="preserve">   use_dc_power       DC 파워 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_dc_delay       DC 안정화 대기 사용 여부 (use_dc_power=T 일 때만 의미 있음)</t>
+          <t xml:space="preserve">   dc_power           DC 파워 [W]. use_dc_power=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_rf_power       RF 파워 사용 여부</t>
+          <t xml:space="preserve">   use_dc_delay       DC 안정화 대기 사용 여부 (use_dc_power=T 일 때만 의미 있음)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rf_power           RF 파워 [W]. use_rf_power=T 면 0 보다 커야 합니다.</t>
+          <t xml:space="preserve">   use_rf_power       RF 파워 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      ※ RF Offset / Param 은 레시피가 아니라 프로그램 화면의 값을 씁니다.</t>
+          <t xml:space="preserve">   rf_power           RF 파워 [W]. use_rf_power=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_rf_pulse       RF Pulse(CESAR) 사용 여부</t>
+          <t xml:space="preserve">                      ※ RF Offset / Param 은 레시피가 아니라 프로그램 화면의 값을 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rf_pulse_power     RF Pulse 파워 [W]. use_rf_pulse=T 면 0 보다 커야 합니다.</t>
+          <t xml:space="preserve">   use_rf_pulse       RF Pulse(CESAR) 사용 여부</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      상한은 config_user.json 의 RFPULSE_MAX_POWER (현재 600W) 입니다.</t>
+          <t xml:space="preserve">   rf_pulse_power     RF Pulse 파워 [W]. use_rf_pulse=T 면 0 보다 커야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rf_pulse_freq      펄스 주파수 [kHz]  장비 범위 0.001~30 kHz (CESAR 1310)</t>
+          <t xml:space="preserve">                      상한은 config_user.json 의 RFPULSE_MAX_POWER (현재 600W) 입니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   rf_pulse_duty      펄스 듀티 [%]  1~99 %. 주파수가 높을수록 범위가 좁아짐(30 kHz 에서는 40~60 %)</t>
+          <t xml:space="preserve">   rf_pulse_freq      펄스 주파수 [kHz]  장비 범위 0.001~30 kHz (CESAR 1310)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ use_rf_power / use_rf_pulse / use_dc_power 는 서로 독립이며 동시에 켤 수 있습니다.</t>
+          <t xml:space="preserve">   rf_pulse_duty      펄스 듀티 [%]  1~99 %. 주파수가 높을수록 범위가 좁아짐(30 kHz 에서는 40~60 %)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     RF power 는 PLC DAC, RF Pulse 는 CESAR 로 서로 다른 장비이고,</t>
+          <t xml:space="preserve">   ★ use_rf_power / use_rf_pulse / use_dc_power 는 서로 독립이며 동시에 켤 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     화면 칸도 ChK_log.csv 컬럼도 각자 따로 갖습니다.</t>
+          <t xml:space="preserve">     RF power 는 PLC DAC, RF Pulse 는 CESAR 로 서로 다른 장비이고,</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ rf_pulse_freq / rf_pulse_duty 를 비우면 장비에 현재 설정된 값을 그대로 씁니다.</t>
+          <t xml:space="preserve">     화면 칸도 ChK_log.csv 컬럼도 각자 따로 갖습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     이때도 공정 로그와 ChK_log.csv 에는 장비에서 되읽은 실제 값이 남습니다.</t>
+          <t xml:space="preserve">   ★ rf_pulse_freq / rf_pulse_duty 를 비우면 장비에 현재 설정된 값을 그대로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ 이 4개 컬럼이 아예 없는 옛 레시피는 자동으로 펄스 미사용이 됩니다.</t>
+          <t xml:space="preserve">     이때도 공정 로그와 ChK_log.csv 에는 장비에서 되읽은 실제 값이 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ ChK_log.csv 에는 RF Pulse 전용 4컬럼이 따로 남습니다:</t>
+          <t xml:space="preserve">   ★ 이 4개 컬럼이 아예 없는 옛 레시피는 자동으로 펄스 미사용이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     "RF Pulse: For.P" / "RF Pulse: Ref. P" (계측 평균), "RF Pulse: Freq[kHz]" / "RF Pulse: Duty[%]" (설정값)</t>
+          <t xml:space="preserve">   ★ ChK_log.csv 에는 RF Pulse 전용 4컬럼이 따로 남습니다:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     기존 "RF: For.P" / "RF: Ref. P" 는 계속 RF power(PLC DAC) 전용입니다.</t>
+          <t xml:space="preserve">     "RF Pulse: For.P" / "RF Pulse: Ref. P" (계측 평균), "RF Pulse: Freq[kHz]" / "RF Pulse: Duty[%]" (설정값)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
+          <t xml:space="preserve">     기존 "RF: For.P" / "RF: Ref. P" 는 계속 RF power(PLC DAC) 전용입니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   gun1 / gun2        건 셔터 사용 여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   G1 Target / G2 Target   타겟 이름(문자열). 제어에는 쓰이지 않고 로그·ERP 보고에만 남습니다.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="n"/>
-    </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>■ 히터 컬럼 3개</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
+          <t xml:space="preserve">   use_heater    T 이면 이 공정에서 히터를 사용합니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
+          <t xml:space="preserve">   heater_temp   목표 온도 [°C]. 0 초과 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+          <t xml:space="preserve">   heater_ramp   승온 속도 [°C/min]. 비우면 기본값 12.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">                 6 미만은 6 으로 자동 보정, 60 초과는 오류입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">                 PLC 램프는 1카운트/초 = 6°C/min 단위라 6의 배수로 반올림됩니다 (10 → 12).</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ 히터 레시피(히터 전용 파일)에 있는 '느린 램프(6 미만)' 는 공정 레시피에는 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="7" t="n"/>
-    </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>■ 히터를 쓰면 공정이 이 순서로 진행됩니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
+          <t xml:space="preserve">   1. 이전 공정 잔류 방지 — DC / RF Power OFF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
+          <t xml:space="preserve">   2. 각 채널 Flow OFF → MFC 메인 밸브 Open  (배기를 최대로 열어 둡니다)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
+          <t xml:space="preserve">   3. 히터 램프 속도 · 목표 온도를 PLC 에 보내고 승온 시작</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
+          <t xml:space="preserve">      ★ 가스를 넣기 전, 고진공 상태에서 올립니다. 아웃가싱이 배기로 빠진 뒤에</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
+          <t xml:space="preserve">        공정 가스를 도입하기 위해서입니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
+          <t xml:space="preserve">   4. 도달 대기 — 램프가 최종 목표에 닿고, 현재 온도가 목표 ±1.0°C 안에</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
+          <t xml:space="preserve">      60초 연속 머물면 '도달' 로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
+          <t xml:space="preserve">   5. 도달한 뒤에 MFC / Power Supply 영점 → 가스 밸브 Open → 유량 설정 · Flow ON</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   6. 압력 제어(SP1) → 건 셔터 → 파워 → shutter_delay → process_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   7. 공정이 끝나거나 STOP 을 누르면 히터가 자동으로 꺼지고, 램프 속도도 기본값으로 돌아갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ 스텝이 끝날 때마다 히터가 꺼집니다. 다음 스텝이 같은 온도를 써도 처음부터 다시 승온합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
+          <t xml:space="preserve">     연속 스텝에서 온도를 계속 유지하려면, 공정 레시피의 히터 칸은 비워 두고</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">     히터 전용 레시피를 따로 돌리세요 (두 레시피는 동시에 돌아갑니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">     단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="n"/>
-    </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
-        </is>
-      </c>
+      <c r="A67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   ※ 히터는 진공 인터락이 걸려 있어 진공이 잡히기 전에는 켜지지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">      그래서 '배기 전 예열' 은 불가능하고, 위 3번이 가능한 가장 빠른 시점입니다.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="7" t="n"/>
-    </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>■ 도달 대기 타임아웃</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   기본 5400초(90분). 예상 승온 시간 + 30분 이 그보다 크면 그쪽을 씁니다 (최대 12시간).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   넘기면 '히터 승온 timeout' 으로 그 공정을 중단합니다.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="7" t="n"/>
-    </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>■ 승온에 걸리는 시간 (상온 25°C 출발, 설정값 기준 계산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
+          <t xml:space="preserve">        목표        12°C/min      6°C/min</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
+          <t xml:space="preserve">        150°C        11.3분        20.8분</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
+          <t xml:space="preserve">        300°C        23.8분        45.8분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
+          <t xml:space="preserve">        400°C        32.1분        62.5분</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
+          <t xml:space="preserve">        600°C        48.8분        95.8분</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+          <t xml:space="preserve">        700°C        57.1분       112.5분</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   목표 직전 10°C 는 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다. 위 값에 포함돼 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   → 승온 시간은 process_time 과 별개로 전체 소요에 그대로 더해집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">   ※ 2026-09-01 실측(상온→300°C 약 45분)은 DAC 상한이 600 이던 시절 파워가 모자라</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">     램프가 뒤처졌던 값입니다. 상한을 1200 으로 올린 뒤로는 설정 램프를 따라갑니다(2026-09-02 600°C 확인).</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="7" t="n"/>
-    </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>■ 저장할 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
+          <t xml:space="preserve">   · 이 파일 그대로 .xlsx 로 저장해서 프로그램의 [Select File] 로 열면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+          <t xml:space="preserve">   · .csv 로 저장해도 동작합니다 (헤더 이름만 같으면 됩니다, UTF-8).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">   · 시트가 여러 개면 'Recipe' 시트를 먼저 찾고, 없으면 첫 번째 시트를 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · 레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행은 넣지 마세요.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="7" t="n"/>
-    </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="A92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>작성 2026-09-04 · 관련 설정: config_user.json 의 HEATER_* 항목</t>
         </is>

--- a/recipes/Chamber-K 공정레시피 샘플.xlsx
+++ b/recipes/Chamber-K 공정레시피 샘플.xlsx
@@ -1157,7 +1157,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   base_pressure      베이스 압력 [Torr]. 가스를 넣기 전 이온 게이지로 이 값 이하가 될 때까지 기다립니다. 비우거나 열이 없으면 1E-5, 0 이면 대기 생략, 1E-9 ~ 1E-3 (1e-5 / 1.0E-05 / 숫자 모두 가능).</t>
+          <t xml:space="preserve">   base_pressure      베이스 압력 [Torr]. 비우거나 열이 없거나 0 이면 베이스 대기 안 함(이온 게이지 사용 안 함). 값이 있으면 1E-9 ~ 1E-3 Torr — 가스를 넣기 전 이온 게이지로 이 값 이하가 될 때까지 기다립니다 (1e-5 / 1.0E-05 / 숫자 모두 가능).</t>
         </is>
       </c>
     </row>
